--- a/AAII_Financials/Yearly/THO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/THO_YR_FIN.xlsx
@@ -656,223 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44773</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44408</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44043</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43677</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43312</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42947</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42582</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42216</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41851</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41486</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41121</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9608100</v>
+      </c>
+      <c r="E8" s="3">
         <v>9579500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10043400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11121600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16312500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12317400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8167900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7864800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8328900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7247000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4582100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4006800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3525500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3241800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2639800</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8395500</v>
+      </c>
+      <c r="E9" s="3">
         <v>8238800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8591400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9525300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13506500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10422400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7049700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6830200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7164200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6203400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3855800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3449300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3055100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2817300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2320300</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1212600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1340600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1452000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1596400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2806000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1895000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1118200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1034500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1164700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1043600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>726300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>557500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>470400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>424500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>319500</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -891,37 +903,38 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E12" s="3">
         <v>48600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>49400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>36600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>39000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>19100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2000</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -938,9 +951,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,20 +1002,23 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-5500</v>
+        <v>-28900</v>
       </c>
       <c r="E14" s="3">
-        <v>6700</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+        <v>-36600</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-9600</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1007,84 +1026,90 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>10100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>176300</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>9100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E15" s="3">
         <v>119000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>132500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>140800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>156900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>117200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>97200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>75600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>55100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>63900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>28000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>10500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>10700</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1100,104 +1125,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9273700</v>
+        <v>9411100</v>
       </c>
       <c r="E17" s="3">
-        <v>9612800</v>
+        <v>9280400</v>
       </c>
       <c r="F17" s="3">
+        <v>9619500</v>
+      </c>
+      <c r="G17" s="3">
         <v>10536100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14779900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11409500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7781100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7441900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7696800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6690600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4198800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3713900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3272600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3019800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2474400</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>305700</v>
+        <v>197100</v>
       </c>
       <c r="E18" s="3">
-        <v>430600</v>
+        <v>299100</v>
       </c>
       <c r="F18" s="3">
+        <v>423900</v>
+      </c>
+      <c r="G18" s="3">
         <v>585500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1532600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>907900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>386900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>422800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>632100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>556400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>383300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>292900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>252800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>222000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>165400</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1216,38 +1248,39 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-33400</v>
+        <v>-49600</v>
       </c>
       <c r="E20" s="3">
-        <v>-13600</v>
+        <v>-9000</v>
       </c>
       <c r="F20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-11300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-17300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-30300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1263,87 +1296,93 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>458200</v>
+        <v>358800</v>
       </c>
       <c r="E21" s="3">
-        <v>576700</v>
+        <v>427000</v>
       </c>
       <c r="F21" s="3">
+        <v>560500</v>
+      </c>
+      <c r="G21" s="3">
         <v>737600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1706900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1055300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>484400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>496600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>691200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>654600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>435900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>324300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>278700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>247000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>190400</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E22" s="3">
         <v>61200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>100000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>97400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>90100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>93500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>107300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>68100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5200</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1359,105 +1398,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>238700</v>
+      </c>
+      <c r="E23" s="3">
         <v>296200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>348800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>499400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1459900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>844600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>272900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>184700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>633000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>556400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>383300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>292900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>252800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>222000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>165400</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E24" s="3">
         <v>39600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>83400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>125100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>321600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>183700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>51500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>52200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>202900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>182100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>125300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>90900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>77300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>70300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>54000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1503,105 +1551,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>174700</v>
+      </c>
+      <c r="E26" s="3">
         <v>256600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>265400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>374200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1138200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>660900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>221400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>132500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>430200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>374300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>258000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>202000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>175500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>151700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>111400</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>177500</v>
+      </c>
+      <c r="E27" s="3">
         <v>258600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>265300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>374300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1137800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>659900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>223000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>133300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>430100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>374300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>258000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>202000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>175500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>151700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>111400</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1647,9 +1704,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1681,23 +1741,26 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-1500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-2600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>3500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>10300</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1743,9 +1806,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1791,39 +1857,42 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>33400</v>
+        <v>49600</v>
       </c>
       <c r="E32" s="3">
-        <v>13600</v>
+        <v>9000</v>
       </c>
       <c r="F32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G32" s="3">
         <v>11300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>17300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>30300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -1839,57 +1908,63 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>177500</v>
+      </c>
+      <c r="E33" s="3">
         <v>258600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>265300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>374300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1137800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>659900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>223000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>133300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>430200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>374300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>256500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>199400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>179000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>152900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>121700</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1935,110 +2010,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>177500</v>
+      </c>
+      <c r="E35" s="3">
         <v>258600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>265300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>374300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1137800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>659900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>223000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>133300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>430200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>374300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>256500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>199400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>179000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>152900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>121700</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44773</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44408</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44043</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43677</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43312</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42947</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42582</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42216</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41851</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41486</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41121</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2057,8 +2141,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2077,56 +2162,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>482000</v>
+      </c>
+      <c r="E41" s="3">
         <v>586600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>501300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>441200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>311600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>445900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>538500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>425600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>275200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>223300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>209900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>183500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>289300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>236600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>218600</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2170,347 +2259,371 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>35000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700900</v>
+      </c>
+      <c r="E43" s="3">
         <v>707400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>700900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>643200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>944200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>949900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>814200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>716200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>487200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>484800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>392500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>278100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>281200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>252800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>233100</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1423100</v>
+      </c>
+      <c r="E44" s="3">
         <v>1351800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1366600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1653100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1754800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1369400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>716300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>828000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>537900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>460500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>403900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>246100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>216400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>153000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>186100</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E45" s="3">
         <v>132200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>81200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>56100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>52000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>30400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>41900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>68200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>57100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>188300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>47100</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2739900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2778000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2650000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2793600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3062500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2803500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2102300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2037400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1311700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1180200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1016900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>775800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>844000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>830700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>684900</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E47" s="3">
         <v>136800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>137300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>126900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10800</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>46200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>48500</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>9000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>25300</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1309500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1315700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1390700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1387800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1258200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1185100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1107600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1092500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>522100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>425200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>344300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>234000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>169900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>143800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>164400</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2600800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2599900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2648100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2797400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2921600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2500400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2391300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2328800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>766000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>821200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>885100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>481600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>376400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>335900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>473700</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2556,9 +2669,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2604,57 +2720,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>238400</v>
+      </c>
+      <c r="E52" s="3">
         <v>199300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>166300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>149400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>141200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>116800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>81700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>69800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>52000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>131400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>79300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>21100</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2700,57 +2822,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6956200</v>
+      </c>
+      <c r="E54" s="3">
         <v>7065300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7020800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7260800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7408100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6654100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5771500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5660400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2778700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2557900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2325500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1503200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1408700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1328300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1243100</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2769,8 +2897,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2789,85 +2918,89 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>740500</v>
+      </c>
+      <c r="E57" s="3">
         <v>738100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>628100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>736300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>822400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>915000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>636500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>551800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>287000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>328600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>263800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>162600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>164600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>135000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>143100</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E58" s="3">
         <v>16400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>44900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>23400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>22400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -2881,144 +3014,153 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>401400</v>
+      </c>
+      <c r="E59" s="3">
         <v>416200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>478700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>538000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>447800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>407700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>525600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>585800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>302100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>452400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>387900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>215700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>206100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>226600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>168000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1550100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1584700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1567000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1716500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1755900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1794800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1515300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1448300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>769300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>781000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>651700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>378300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>370700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>361700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>311100</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>895700</v>
+      </c>
+      <c r="E61" s="3">
         <v>950600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1135100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1330800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1792500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1633400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1686000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1890500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>145000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>360000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3028,57 +3170,63 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200600</v>
+      </c>
+      <c r="E62" s="3">
         <v>186000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>170200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>154500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>143100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>164200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>100800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>90700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>71600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>55300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>48600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>59700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>60300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>74000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>81100</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3124,9 +3272,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3172,9 +3323,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3220,57 +3374,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2696200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2775700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2946800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3277400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3807500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3706000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3425900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3565200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>840900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>981400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1060200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>438100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>431000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>435700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>392200</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3289,8 +3449,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3336,9 +3497,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3384,9 +3548,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3432,9 +3599,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3480,57 +3650,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4475900</v>
+      </c>
+      <c r="E72" s="3">
         <v>4407200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4254700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4091600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3813300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2770400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2201300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2066700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2023000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1670800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1366000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1172400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1030400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>953700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>918600</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3576,9 +3752,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3624,9 +3803,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3672,57 +3854,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4261500</v>
+      </c>
+      <c r="E76" s="3">
         <v>4288500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4067400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3976000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3592900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2921800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2319800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2084400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1937700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1576500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1265200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1065200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>977700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>892600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>850800</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3768,110 +3956,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44773</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44408</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44043</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43677</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43312</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42947</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42582</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42216</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41851</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41486</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41121</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>177500</v>
+      </c>
+      <c r="E81" s="3">
         <v>258600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>265300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>374300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1137800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>659900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>223000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>133300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>430200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>374300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>256500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>199400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>179000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>152900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>121700</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3890,56 +4087,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>154200</v>
+      </c>
+      <c r="E83" s="3">
         <v>152200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>144600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>136100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>127500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>113400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>98900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>73100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>98300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>52600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>31400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25800</v>
-      </c>
-      <c r="P83" s="3">
-        <v>25000</v>
       </c>
       <c r="Q83" s="3">
         <v>25000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>25000</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3985,9 +4186,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4033,9 +4237,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4081,9 +4288,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4129,9 +4339,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4177,57 +4390,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>321200</v>
+      </c>
+      <c r="E89" s="3">
         <v>577900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>545500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>981600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>990100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>526500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>540900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>508000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>466500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>419300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>341200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>247900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>149300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>145100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>118800</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4246,56 +4465,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-152400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-123000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-139600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-208200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-242400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-128800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-106700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-130200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-138200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-115000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-52000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-42300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-30400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-24300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10100</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4341,9 +4564,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4389,57 +4615,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-125400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-64500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-146800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-222500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1049300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-428500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-84200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1865500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-183500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-116700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-601500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-235000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7900</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4458,56 +4690,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>108800</v>
+      </c>
+      <c r="E96" s="3">
         <v>106100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>102100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>96000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>94900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>90800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>88300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>84100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>78000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-69400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-63000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-57400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-102300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-117700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-32300</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4553,9 +4789,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4601,9 +4840,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4649,83 +4891,89 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-296600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-426300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-337700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-635700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-47800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-188400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-392900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1539100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-231000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-289300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>286700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-118800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-99500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-113100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-107800</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-30200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>26300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5600</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
@@ -4742,58 +4990,64 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-104600</v>
+      </c>
+      <c r="E102" s="3">
         <v>85300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>60100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>129700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-137200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-92700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>90100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>176000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>52000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>26400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-105900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>52700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>18000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3200</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
